--- a/docs/downloads/04/tbl_other_chars_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_chars_alaotra_ambodivoara.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -633,12 +633,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -653,7 +647,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D14">
@@ -702,12 +696,6 @@
           <t>Veuf(ve)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -791,14 +779,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D20">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E20">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="21">
@@ -814,14 +802,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="E21">
-        <v>2.4</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="22">
@@ -837,36 +825,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D22">
-        <v>272</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>15</v>
-      </c>
-      <c r="E23">
         <v>2</v>
       </c>
     </row>
